--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/14,07,26 ПОКОМ КИ/машины ПОКОМ КИ.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/14,07,26 ПОКОМ КИ/машины ПОКОМ КИ.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\14,07,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A3FEC4-03FC-45F7-9595-33399E2C700F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71A7B13-CA20-49CD-9905-ED8FEB9723CD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -169,7 +169,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -212,6 +212,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="25">
     <border>
@@ -559,7 +565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -626,6 +632,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1068,13 +1083,13 @@
       <c r="E3" s="6"/>
       <c r="F3" s="3"/>
       <c r="G3" s="7"/>
-      <c r="H3" s="19">
+      <c r="H3" s="47">
         <v>5984</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="48">
         <v>6689</v>
       </c>
-      <c r="J3" s="21">
+      <c r="J3" s="49">
         <v>11</v>
       </c>
       <c r="K3" s="6"/>
@@ -1113,19 +1128,19 @@
       <c r="E4" s="4"/>
       <c r="F4" s="2"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="24"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="52"/>
       <c r="K4" s="4"/>
       <c r="L4" s="2"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="4">
+      <c r="N4" s="50">
         <v>17202</v>
       </c>
-      <c r="O4" s="2">
+      <c r="O4" s="51">
         <v>19263</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P4" s="52">
         <v>30</v>
       </c>
       <c r="Q4" s="4"/>
@@ -1164,28 +1179,28 @@
       <c r="E5" s="4"/>
       <c r="F5" s="2"/>
       <c r="G5" s="5"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="4">
+      <c r="H5" s="50"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="50">
         <v>17206</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="51">
         <v>19182</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="52">
         <v>31</v>
       </c>
       <c r="N5" s="4"/>
       <c r="O5" s="2"/>
       <c r="P5" s="5"/>
-      <c r="Q5" s="4">
+      <c r="Q5" s="50">
         <v>12212</v>
       </c>
-      <c r="R5" s="2">
+      <c r="R5" s="51">
         <v>13444</v>
       </c>
-      <c r="S5" s="5">
+      <c r="S5" s="52">
         <v>21</v>
       </c>
       <c r="T5" s="4"/>
@@ -1221,13 +1236,13 @@
       <c r="E6" s="4"/>
       <c r="F6" s="2"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="22">
+      <c r="H6" s="50">
         <v>11437</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="51">
         <v>12679</v>
       </c>
-      <c r="J6" s="24">
+      <c r="J6" s="52">
         <v>20</v>
       </c>
       <c r="K6" s="4"/>
@@ -1236,9 +1251,9 @@
       <c r="N6" s="4"/>
       <c r="O6" s="2"/>
       <c r="P6" s="5"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="5"/>
+      <c r="Q6" s="50"/>
+      <c r="R6" s="51"/>
+      <c r="S6" s="52"/>
       <c r="T6" s="4"/>
       <c r="U6" s="2"/>
       <c r="V6" s="5"/>
@@ -1269,9 +1284,9 @@
       <c r="N7" s="4"/>
       <c r="O7" s="2"/>
       <c r="P7" s="5"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="5"/>
+      <c r="Q7" s="50"/>
+      <c r="R7" s="51"/>
+      <c r="S7" s="52"/>
       <c r="T7" s="4"/>
       <c r="U7" s="2"/>
       <c r="V7" s="5"/>
@@ -1302,9 +1317,9 @@
       <c r="N8" s="4"/>
       <c r="O8" s="2"/>
       <c r="P8" s="5"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="5"/>
+      <c r="Q8" s="50"/>
+      <c r="R8" s="51"/>
+      <c r="S8" s="52"/>
       <c r="T8" s="4"/>
       <c r="U8" s="2"/>
       <c r="V8" s="5"/>
@@ -1335,9 +1350,9 @@
       <c r="N9" s="4"/>
       <c r="O9" s="2"/>
       <c r="P9" s="5"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="5"/>
+      <c r="Q9" s="50"/>
+      <c r="R9" s="51"/>
+      <c r="S9" s="52"/>
       <c r="T9" s="4"/>
       <c r="U9" s="2"/>
       <c r="V9" s="5"/>
@@ -1368,9 +1383,9 @@
       <c r="N10" s="9"/>
       <c r="O10" s="10"/>
       <c r="P10" s="11"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="11"/>
+      <c r="Q10" s="44"/>
+      <c r="R10" s="45"/>
+      <c r="S10" s="46"/>
       <c r="T10" s="9"/>
       <c r="U10" s="10"/>
       <c r="V10" s="11"/>
@@ -1407,9 +1422,9 @@
       <c r="N11" s="9"/>
       <c r="O11" s="10"/>
       <c r="P11" s="11"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="11"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="45"/>
+      <c r="S11" s="46"/>
       <c r="T11" s="25">
         <v>3425</v>
       </c>
@@ -1446,9 +1461,9 @@
       <c r="N12" s="9"/>
       <c r="O12" s="10"/>
       <c r="P12" s="11"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="11"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="45"/>
+      <c r="S12" s="46"/>
       <c r="T12" s="9"/>
       <c r="U12" s="10"/>
       <c r="V12" s="11"/>
@@ -1479,9 +1494,9 @@
       <c r="N13" s="9"/>
       <c r="O13" s="10"/>
       <c r="P13" s="11"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="11"/>
+      <c r="Q13" s="44"/>
+      <c r="R13" s="45"/>
+      <c r="S13" s="46"/>
       <c r="T13" s="9"/>
       <c r="U13" s="10"/>
       <c r="V13" s="11"/>
@@ -1518,9 +1533,9 @@
       <c r="N14" s="9"/>
       <c r="O14" s="10"/>
       <c r="P14" s="11"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="11"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="45"/>
+      <c r="S14" s="46"/>
       <c r="T14" s="9"/>
       <c r="U14" s="10"/>
       <c r="V14" s="11"/>
@@ -1563,9 +1578,9 @@
       <c r="N15" s="9"/>
       <c r="O15" s="10"/>
       <c r="P15" s="11"/>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="11"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="45"/>
+      <c r="S15" s="46"/>
       <c r="T15" s="9"/>
       <c r="U15" s="10"/>
       <c r="V15" s="11"/>
@@ -1602,9 +1617,9 @@
       <c r="N16" s="9"/>
       <c r="O16" s="10"/>
       <c r="P16" s="11"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="11"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="45"/>
+      <c r="S16" s="46"/>
       <c r="T16" s="9"/>
       <c r="U16" s="10"/>
       <c r="V16" s="11"/>
@@ -1629,13 +1644,13 @@
       <c r="D17" s="27">
         <v>12</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="44">
         <v>7186</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="45">
         <v>7792</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="46">
         <v>12</v>
       </c>
       <c r="H17" s="25"/>
@@ -1647,9 +1662,9 @@
       <c r="N17" s="9"/>
       <c r="O17" s="10"/>
       <c r="P17" s="11"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="11"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="45"/>
+      <c r="S17" s="46"/>
       <c r="T17" s="9"/>
       <c r="U17" s="10"/>
       <c r="V17" s="11"/>
@@ -1674,13 +1689,13 @@
       <c r="D18" s="27">
         <v>13</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="44">
         <v>7852</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="45">
         <v>8549</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="46">
         <v>13</v>
       </c>
       <c r="H18" s="25"/>
@@ -1692,9 +1707,9 @@
       <c r="N18" s="9"/>
       <c r="O18" s="10"/>
       <c r="P18" s="11"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="11"/>
+      <c r="Q18" s="44"/>
+      <c r="R18" s="45"/>
+      <c r="S18" s="46"/>
       <c r="T18" s="9"/>
       <c r="U18" s="10"/>
       <c r="V18" s="11"/>
@@ -1731,13 +1746,13 @@
       <c r="N19" s="9"/>
       <c r="O19" s="10"/>
       <c r="P19" s="11"/>
-      <c r="Q19" s="22">
+      <c r="Q19" s="50">
         <v>4920</v>
       </c>
-      <c r="R19" s="26">
+      <c r="R19" s="45">
         <v>5421</v>
       </c>
-      <c r="S19" s="27">
+      <c r="S19" s="46">
         <v>9</v>
       </c>
       <c r="T19" s="9"/>
